--- a/business_forms/047_customer_advocacy_program_application_form--business_forms.xlsx
+++ b/business_forms/047_customer_advocacy_program_application_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'executive'}</t>
+          <t>executive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Executive'}</t>
+          <t>Executive</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'1-10_employees'}</t>
+          <t>1-10_employees</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '1-10 employees'}</t>
+          <t>1-10 employees</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'11-50_employees'}</t>
+          <t>11-50_employees</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '11-50 employees'}</t>
+          <t>11-50 employees</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'51-100_employees'}</t>
+          <t>51-100_employees</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '51-100 employees'}</t>
+          <t>51-100 employees</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'101-200_employees'}</t>
+          <t>101-200_employees</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '101-200 employees'}</t>
+          <t>101-200 employees</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'201-500_employees'}</t>
+          <t>201-500_employees</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': '201-500 employees'}</t>
+          <t>201-500 employees</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'501-1000_employees'}</t>
+          <t>501-1000_employees</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': '501-1000 employees'}</t>
+          <t>501-1000 employees</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'1001+_employees'}</t>
+          <t>1001+_employees</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': '1001+ employees'}</t>
+          <t>1001+ employees</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'video_call'}</t>
+          <t>video_call</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Video Call'}</t>
+          <t>Video Call</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
